--- a/光伏配储项目/电价数据/2026/横门B厂.xlsx
+++ b/光伏配储项目/电价数据/2026/横门B厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.28785</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.65649</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9767899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8171499999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.65496</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45929</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.47212</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5344099999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.72161</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.58957</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.5884199999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.6228899999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.6436499999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.83065</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.79172</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.87913</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.70709</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.58778</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7420399999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.78462</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.14953</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.48933</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.64593</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.66049</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.66011</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.8063899999999999</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.75019</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.91403</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.13784</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.73194</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.43062</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.66555</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.00093</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.03978</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.05238</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.10128</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.46253</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.8680399999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.08073</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.6973</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.36478</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.14032</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.1286</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.63521</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.28572</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.23175</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.15503</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.7355700000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.05586</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.00175</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.14807</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53774</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52276</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49902</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47323</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42185</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5704199999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.83305</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7324299999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47347</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.81014</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.0387</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.66162</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.07026</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.93123</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.81836</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.61542</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.50857</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5126900000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.5952200000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.9683200000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.06662</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.28355</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.99252</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.45095</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.02112</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.69645</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.12501</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.9846900000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.21459</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.59937</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.5638099999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5338200000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58947</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.93002</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.00501</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.00956</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.01831</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8198799999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.20844</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20861</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18206</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.64406</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.02496</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20301</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.97348</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.26346</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.12443</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.73264</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.00902</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.52816</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26114</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.68161</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76834</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.92752</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.52236</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.56608</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4704700000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.40195</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.62387</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.7913</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.05058</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6476900000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.66859</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6118300000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.65818</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6744</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.07845</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.34806</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.62242</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.05873</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.39725</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.15193</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.00515</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7166399999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7765</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.99109</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.9976900000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.81648</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.54164</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.64737</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.06313</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.9126000000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.00155</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.17984</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.04113</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.01307</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18636</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.18419</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.15781</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.54895</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.96412</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.98946</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.47412</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.89311</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.65765</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.96274</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.98385</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.96984</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.04309</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.04252</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.08935</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.86063</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.68129</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.63412</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.49101</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9480700000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.56453</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.48729</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.5349299999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.72778</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.43709</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.72523</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.43837</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6254999999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.6916</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.8865499999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.03546</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.02547</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.7213200000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.40707</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.62883</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.85102</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.72482</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.02488</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.38437</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.73652</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.79189</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.00226</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.59446</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.14571</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48368</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.5794400000000001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.8527</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.98588</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.16899</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.02137</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.82455</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.9815199999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.94548</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.04494</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.27234</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.69445</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.99249</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.7622000000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.92316</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.04123</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.06251</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.98997</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.10937</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9910399999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.12844</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.62115</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.11236</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.16031</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18657</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.05912</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.00781</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.99251</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.97074</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.10968</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.63303</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.63209</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31973</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7138099999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.47314</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.48384</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.65546</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.77703</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.5608200000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.64147</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.66414</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.77703</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.6462</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.49282</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.43165</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.00801</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.21956</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18695</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.20987</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.51662</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.4534</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.5559700000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5346599999999999</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.47788</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.46149</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.05636</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.82377</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8429</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.54826</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.52884</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06612999999999999</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.2779700000000001</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04734</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04884</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03259</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.25583</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.07146</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.11027</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.00742</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.27429</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.27613</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.17585</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.19359</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33278</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.42594</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.22848</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.25511</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.24894</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.6396900000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.75286</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.5942499999999999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5937</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.61988</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.6619400000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.82985</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.66495</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.6498200000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.77884</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.5283099999999999</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.47831</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.47022</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.04523</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.6733899999999999</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.6247699999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.55984</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48026</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.6754199999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.77778</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7440800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5522100000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.6831199999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.9588300000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.28936</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.30999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.07047</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.72881</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.68367</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.26514</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.95235</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.65625</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.28307</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.66395</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.34724</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7189</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80075</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50231</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41153</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21864</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54114</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59927</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5581199999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.08725</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6057899999999999</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49327</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.53351</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.60707</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.91976</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.31938</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.28281</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.29109</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80838</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5578500000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.62479</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5141699999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.82959</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7302000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.67726</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.59226</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.8292999999999999</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.6963200000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.43557</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5525599999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.48079</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.5354099999999999</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.54799</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.54652</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.47456</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.5320199999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5591900000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.65279</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.54652</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.64118</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.5477300000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.55935</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.54338</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.53034</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.52667</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.45982</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9511000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.50702</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.53718</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.73619</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.91843</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.8873</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.47287</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.05572</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.73027</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.8227000000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.73748</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.57289</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.6938500000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.92901</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.73594</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.65426</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.75449</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.97756</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.67231</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.6948200000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.65132</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.6430900000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.25438</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.23887</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.46162</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49443</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.17561</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.48567</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70269</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79414</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6489299999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58282</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.67488</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.64144</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.04149</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.84839</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.57789</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.43703</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.63207</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.43349</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.24057</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.47279</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.03851</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.48565</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.8289299999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.03893</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.07543</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.04709</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.04545</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.8894299999999999</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6269600000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.53559</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.4084</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.23549</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.51525</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.79089</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.39813</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.68228</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.95801</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.97836</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.8114400000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.92443</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.87525</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.11714</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.01535</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.74481</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.02233</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.50279</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.8494700000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.90081</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.01894</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.82686</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.86415</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.45132</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.7980700000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.86566</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.92286</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.76849</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.7476699999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.55649</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.97182</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.29534</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.8428099999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.84601</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.6775099999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.64436</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.56743</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.46517</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.47749</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.6758500000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5840299999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6329199999999999</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.86125</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.28797</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.18312</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8610800000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45237</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70704</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.96254</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.2009</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.14828</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.14638</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.55388</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.9509</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9432200000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.93161</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.93252</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.58578</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.52858</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9569099999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.11551</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.76443</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.03494</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.7518</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.61659</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.60659</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.6953</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.8263400000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.31411</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.77481</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.37481</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.48893</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.10388</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.92652</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.60658</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.59158</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.62438</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.63675</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.63182</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.60854</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.63158</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20757</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.66671</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.74723</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.66314</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.67152</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.67893</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.60165</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.71321</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.03403</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.14555</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.65787</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.66552</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.65988</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.74417</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.68905</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.77947</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.64181</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.69961</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.85376</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34018</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.47861</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.01118</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.71611</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.4973</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.44628</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.8883799999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.43797</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.13507</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.91179</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.77538</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.48533</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44147</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34924</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7161900000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.58633</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.48532</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41164</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56716</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.63875</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81721</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46789</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44089</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7699900000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.77667</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.55802</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50485</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7534500000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.77232</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50551</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45365</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.03231</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.51011</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.47824</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.14957</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.11272</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.50636</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.04246</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.21797</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.16582</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8654400000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.36686</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9148099999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.9388500000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.97368</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.68401</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.21429</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.51468</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.09807</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.73775</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.1826</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.00171</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.54992</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46148</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.63986</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.65169</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.79238</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.64528</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.18449</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.25129</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.59652</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.52994</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.24951</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.9463400000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.50015</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.45671</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.49739</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.6487000000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.06384</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.62139</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.78939</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.59068</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.81029</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.76193</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.65509</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.62253</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.12654</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.13003</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.30717</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.10998</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.39643</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.62482</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.68851</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.00411</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.23599</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.91277</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.22865</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.99778</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47597</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.9178999999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.49518</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80779</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.5944299999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.53125</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.98517</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.55043</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.65324</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.76995</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.89542</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.04024</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49595</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.15755</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.53898</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.12113</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5505399999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.47577</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23068</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42944</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.49458</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.48493</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.73365</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.45573</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44185</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.5379400000000001</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.44759</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.45215</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.71982</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.5202899999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02336</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.19816</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.63551</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.77073</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.45387</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.04387</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.27043</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.5992499999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.60902</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.71529</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.70882</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.4944</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.52691</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43909</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.71726</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.48985</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.12237</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.12684</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.08955</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.93359</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.80003</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.12925</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.49065</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.50757</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.45908</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5350199999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.6959099999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.52198</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.50164</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.09605</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.6921499999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.69864</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.52806</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.85203</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.69648</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.5707300000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.69865</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.02089</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.5620599999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.61309</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.08645</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.7400599999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.73088</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.7755700000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.03957</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5804199999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6039099999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.81877</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.43119</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.44767</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.61974</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.43119</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.60002</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.7623</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.9823500000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85378</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.88122</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.3512</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.22522</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.99601</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7239500000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34376</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.77127</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5318200000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7227</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7248</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.54215</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.57409</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5634400000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.51807</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.4333399999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.54115</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8039700000000001</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.05846</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.96949</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.07092</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.61682</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.60577</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.9778600000000001</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.00192</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56674</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.49678</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.52915</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55488</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.51285</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.63279</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.47247</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.99962</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.61019</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.48222</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.4685299999999999</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.48476</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.46924</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5568099999999999</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.48564</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.48744</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.54165</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.63385</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.04172</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.94124</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6372100000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.09143</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.82673</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.63561</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.02737</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.69499</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.48588</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3436</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.48446</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.45867</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6049800000000001</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5516599999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.56797</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8849900000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.03129</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.8791599999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.84027</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.89636</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7888099999999999</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.81529</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.8041699999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.78142</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.7905399999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.56111</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.78427</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.7857999999999999</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.96509</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.77618</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.94656</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.7954199999999999</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7198099999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.7866299999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.50521</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.58892</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.63636</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.69676</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.68788</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.74431</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.79114</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.76964</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.14089</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.00903</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.9457000000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.2602</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.9428200000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.02146</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.84445</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.69149</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.68991</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.76342</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.62161</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70113</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.51152</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.66853</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.64735</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.61314</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.68206</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.62324</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.65474</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.49831</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.48039</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.85205</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.74688</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.8806799999999999</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.72646</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.8986900000000001</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8776900000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.8756900000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.9191</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.93752</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.8486900000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.09028</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.59282</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.6275700000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.62417</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.03756</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.58292</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.58616</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.71408</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.61169</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.71193</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.69454</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.72476</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.70498</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.63433</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.06361</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.04613</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.75356</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.1908</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.18731</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.00261</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.78923</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.9673999999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.10829</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.7621599999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.15217</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.11093</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.51547</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.41856</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.18348</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.18411</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.7830499999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.69333</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.77213</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.72499</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.48837</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8204400000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.33187</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.01659</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9416100000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9685900000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.02396</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.15755</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.02477</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.88709</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69772</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.15003</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.18354</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.18285</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.1744</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.88536</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.71593</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.11714</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.6821</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.12428</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.12455</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52462</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15192</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.65104</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.58358</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.19512</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.80636</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06294</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.91061</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.88466</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.02305</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.08149</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.13279</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.06176</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.07368</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18408</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16904</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.1931</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20689</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.1214</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.17947</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.02265</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.13259</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.11411</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.13991</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.19059</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.20823</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.19138</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.91843</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.60238</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.52224</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5136000000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37623</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7114199999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.33038</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.32883</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.73865</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.08027</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.46952</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.52339</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84982</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.6089600000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6245499999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.57729</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.86363</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.8722000000000001</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.76054</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.91532</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9833500000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.32721</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.41796</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.24245</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.19727</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85449</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.47056</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.51891</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.8528300000000001</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8442799999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.0866</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.79015</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.60317</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.57961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.56684</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.51823</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.60194</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.61041</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.11401</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.37875</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.11125</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.13151</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.12391</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.9872300000000001</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.9634400000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.18298</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.98676</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.07748</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.93576</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.96992</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.19692</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.96141</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.96257</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.96796</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.7946</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80552</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56514</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5604600000000001</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5159900000000001</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55444</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5216499999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50141</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49661</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.50117</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.52351</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.48374</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5297500000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.53438</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.55343</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55547</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.60526</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6369900000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6419900000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.57343</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6758</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60366</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.59378</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.58723</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.61838</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.61533</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.69214</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5014</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37241</v>
       </c>
     </row>
   </sheetData>
